--- a/mode_docx_gen/pmi_mtzt/kzn_modes/КЦН_11.xlsx
+++ b/mode_docx_gen/pmi_mtzt/kzn_modes/КЦН_11.xlsx
@@ -1251,8 +1251,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>gen_pusk_ptoc_lvttoc</t>
+          <t>gen_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
